--- a/lcoe/liquid_fuels/ethanol_upgrade_lcoe/LCOE_ETHANOL_UPGRADE_TEMPLATE.xlsx
+++ b/lcoe/liquid_fuels/ethanol_upgrade_lcoe/LCOE_ETHANOL_UPGRADE_TEMPLATE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/abbie/Desktop/Dolphyn_to_Macro/Dolphyn vs. Macro/Python Codes/lcoe/liquid_fuels/ethanol_upgrade_lcoe/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9928D7C8-9081-C84C-931D-52C55677421E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{594F755D-39C0-294C-88AD-A531BE46EE54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29400" yWindow="500" windowWidth="38400" windowHeight="23500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="29380" yWindow="500" windowWidth="38400" windowHeight="22620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="lc_detailed" sheetId="1" r:id="rId1"/>
@@ -1776,7 +1776,7 @@
         <v>0.185341119</v>
       </c>
       <c r="DF4" s="25">
-        <v>322562.05</v>
+        <v>0</v>
       </c>
       <c r="DG4" s="25">
         <v>176727.97</v>
